--- a/risk_matrix/risk_matrix_2026.xlsx
+++ b/risk_matrix/risk_matrix_2026.xlsx
@@ -27,11 +27,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -68,10 +68,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -502,10 +502,14 @@
       </c>
       <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr"/>
+      <c r="D2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="F2" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
     </row>
@@ -516,17 +520,19 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="D3" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -537,18 +543,20 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
@@ -574,16 +582,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="F6" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
@@ -593,18 +601,24 @@
           <t>Unsuccessful low-level malicious attack</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="D7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F7" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/risk_matrix/risk_matrix_2026.xlsx
+++ b/risk_matrix/risk_matrix_2026.xlsx
@@ -529,10 +529,10 @@
         <v>5</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -546,16 +546,16 @@
         <v>5</v>
       </c>
       <c r="C4" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>6</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>5</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
@@ -582,16 +582,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>3</v>

--- a/risk_matrix/risk_matrix_2026.xlsx
+++ b/risk_matrix/risk_matrix_2026.xlsx
@@ -582,7 +582,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>7</v>

--- a/risk_matrix/risk_matrix_2026.xlsx
+++ b/risk_matrix/risk_matrix_2026.xlsx
@@ -529,7 +529,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>12</v>
@@ -549,7 +549,7 @@
         <v>7</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>41</v>
@@ -585,7 +585,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>5</v>

--- a/risk_matrix/risk_matrix_2026.xlsx
+++ b/risk_matrix/risk_matrix_2026.xlsx
@@ -552,10 +552,10 @@
         <v>14</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>

--- a/risk_matrix/risk_matrix_2026.xlsx
+++ b/risk_matrix/risk_matrix_2026.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not placed" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -66,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -79,6 +80,9 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -502,15 +506,9 @@
       </c>
       <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>6</v>
-      </c>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
@@ -520,21 +518,21 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -543,19 +541,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
@@ -565,8 +563,12 @@
           <t>Coordinated low-level malicious attack</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="B5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
@@ -579,19 +581,17 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="E6" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
@@ -602,22 +602,255 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Impact Type</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Stakeholder</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Classifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Coordinated low-level malicious attack</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Extensive compromise</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Academia/R&amp;D</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Federal government</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Large organisation(s)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Regulated critical infrastructure</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Schools</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Small organisation(s)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>State government</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Supply chain</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Isolated compromise</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Low-level malicious attack</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Unsuccessful low-level malicious attack</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/risk_matrix/risk_matrix_2026.xlsx
+++ b/risk_matrix/risk_matrix_2026.xlsx
@@ -525,7 +525,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>4</v>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">

--- a/risk_matrix/risk_matrix_2026.xlsx
+++ b/risk_matrix/risk_matrix_2026.xlsx
@@ -518,17 +518,17 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>1</v>
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>9</v>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -741,11 +741,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Regulated critical infrastructure</t>
+          <t>Medium-sized organisation(s)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -756,7 +756,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Schools</t>
+          <t>Regulated critical infrastructure</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Small organisation(s)</t>
+          <t>Schools</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -786,7 +786,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>State government</t>
+          <t>Small organisation(s)</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Supply chain</t>
+          <t>State government</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -811,22 +811,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Isolated compromise</t>
+          <t>Insufficient information</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Insufficient information</t>
+          <t>Supply chain</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Low-level malicious attack</t>
+          <t>Isolated compromise</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unsuccessful low-level malicious attack</t>
+          <t>Low-level malicious attack</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/risk_matrix/risk_matrix_2026.xlsx
+++ b/risk_matrix/risk_matrix_2026.xlsx
@@ -525,7 +525,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>3</v>
@@ -550,7 +550,7 @@
         <v>50</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>9</v>
